--- a/estado_cuenta_clientes.xlsx
+++ b/estado_cuenta_clientes.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cartera Clientes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account of statement" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Invoices" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +30,33 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,8 +71,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="009ed1b7"/>
         <bgColor rgb="009ed1b7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCCCCC"/>
+        <bgColor rgb="00CCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFFCC"/>
+        <bgColor rgb="00CCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,9 +118,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -85,6 +139,50 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,283 +550,1447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Order No.</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+          <t>ACCOUNT STATEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Total Invoice Amount:</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$3,472.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Total Payments:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$3,266.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Total Credit Notes:</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$157.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Overdue Balance:</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Total Balance Due:</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>$0.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Intermediary</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Exporter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>AWB</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Invoice Amount USD</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Amount Paid by Customer USD</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Expected Payment Date</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Overdue Days</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Credit Note Number</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Credit Note Amount</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Final Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>729-44581611</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>3472</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>3266.09</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Ecuafields</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>2024-02-12</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>387</v>
+      </c>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>OVERDUE INVOICES SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Invoice Number</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Overdue Days</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Final Amount</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>387</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Total Overdue:</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>OVERALL BALANCE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Intermediary</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Total Invoices</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Total Paid</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Total Credit Notes</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Total Discounts</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="n"/>
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="17" t="n"/>
+      <c r="L21" s="17" t="n"/>
+      <c r="M21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr"/>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Ecuafields</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr"/>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>3472</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>3266.09</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COMPLETE INVOICE LIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Intermediary</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>AWB</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Delivery Date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Days Past Due</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Payment Date</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Invoice Value USD</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Invoice Number</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Invoice Amount USD</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>Amount Paid by Customer USD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Credit Note</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Total CN</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Banking Profit</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Customer Payment Date</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Invoice Status</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>877</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Ams European</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CI_Dorado</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Hfs-100</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>124563589456</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente Pago</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Payment Date</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>Overdue Days</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Credit Note Number</t>
+        </is>
+      </c>
+      <c r="L3" s="17" t="inlineStr">
+        <is>
+          <t>Credit Note Amount</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Final Amount</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Intermediary</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Exporter</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Total Invoices</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Total Paid by Customer</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>Total Banking Profits</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Total Credit Notes</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>Total Discounts</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="1" t="n"/>
+      <c r="A4" s="20" t="inlineStr"/>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Pedido Cancelado</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="20" t="inlineStr"/>
+      <c r="J4" s="20" t="n">
+        <v>205</v>
+      </c>
+      <c r="K4" s="20" t="n"/>
+      <c r="L4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>Cancelada</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Ams European</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CI_Dorado</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="A5" s="22" t="inlineStr"/>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>729-44777994</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>5572</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>3250</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>3239</v>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <v>-24</v>
+      </c>
+      <c r="N5" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr"/>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>729-44776340</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>3944</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>3909</v>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr"/>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>729-44776336</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>3345</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>3310</v>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="23" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M7" s="23" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="N7" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr"/>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>729-44776325</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>5162.5</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>5006.5</v>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="23" t="n">
+        <v>121</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr"/>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>729-44776314</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>4920</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>4866.56</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="23" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M9" s="23" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr"/>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>729-44583442</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>5433</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>3808</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>3773</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr"/>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>729-44582742</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>4620</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>4595</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>729-44581611</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>3472</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>3266.09</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Abono</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr"/>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>729-44581600</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>6272</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>6220.81</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>729-44581596</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>5040</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>5013.2</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr"/>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>729-44581364</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>6204.8</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>6190.08</v>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr"/>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Juan_Matas</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>729-44580955</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>2910.6</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>2898.1</v>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Ecuafields</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="24" t="n">
+        <v>387</v>
+      </c>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>Factura sin valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr"/>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Luz Mery Melo Mejia</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Etnico</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>4644</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>1412.28</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>1621.8</v>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>-209.52</v>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>Pagada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETE INVOICE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Invoiced:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>$54,361.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Payments:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>$53,909.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Credit Notes:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>$301.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Balance:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>$-244.38</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>